--- a/data/single_run/input/components/distances/coordinates_second_test.xlsx
+++ b/data/single_run/input/components/distances/coordinates_second_test.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,26 +413,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>facility_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>y</t>
         </is>
@@ -462,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-64.8</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -471,342 +459,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ccp_br1_bt1_2</t>
+          <t>r1_br1_bt1_1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CCP</t>
+          <t>Role1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-57.17647058823529</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-49.55294117647058</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-41.92941176470588</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-34.30588235294118</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_6</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>-26.68235294117647</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_7</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>-19.05882352941177</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>-11.43529411764706</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt1_9</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>-3.811764705882354</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3.811764705882354</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>11.43529411764706</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_3</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>19.05882352941177</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_4</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>26.68235294117646</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_5</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>34.30588235294117</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_6</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>41.92941176470588</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_7</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>49.55294117647058</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_8</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>57.17647058823529</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>ccp_br1_bt2_9</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CCP</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>64.8</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>r1_br1_bt1_1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>-50.4</v>
-      </c>
-      <c r="D20" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>r1_br1_bt2_1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Role1</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="D21" t="n">
         <v>20</v>
       </c>
     </row>
